--- a/artfynd/A 35314-2025 artfynd.xlsx
+++ b/artfynd/A 35314-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5683,6 +5683,127 @@
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128076199</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tamptjärnsån, Tamptjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>514281</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6742166</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35314-2025 artfynd.xlsx
+++ b/artfynd/A 35314-2025 artfynd.xlsx
@@ -5688,7 +5688,7 @@
         <v>128076199</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 35314-2025 artfynd.xlsx
+++ b/artfynd/A 35314-2025 artfynd.xlsx
@@ -5688,7 +5688,7 @@
         <v>128076199</v>
       </c>
       <c r="B53" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 35314-2025 artfynd.xlsx
+++ b/artfynd/A 35314-2025 artfynd.xlsx
@@ -5688,7 +5688,7 @@
         <v>128076199</v>
       </c>
       <c r="B53" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 35314-2025 artfynd.xlsx
+++ b/artfynd/A 35314-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017045</v>
+        <v>125017015</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514340</v>
+        <v>514225</v>
       </c>
       <c r="R2" t="n">
-        <v>6741996</v>
+        <v>6741799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017084</v>
+        <v>125017021</v>
       </c>
       <c r="B3" t="n">
-        <v>96395</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514370</v>
+        <v>514291</v>
       </c>
       <c r="R3" t="n">
-        <v>6742063</v>
+        <v>6741927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,50 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017029</v>
+        <v>125017022</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514393</v>
+        <v>514283</v>
       </c>
       <c r="R4" t="n">
-        <v>6741939</v>
+        <v>6741836</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017043</v>
+        <v>125017025</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514354</v>
+        <v>514390</v>
       </c>
       <c r="R5" t="n">
-        <v>6742044</v>
+        <v>6741952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017074</v>
+        <v>125017083</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514374</v>
+        <v>514373</v>
       </c>
       <c r="R6" t="n">
-        <v>6741981</v>
+        <v>6741951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017044</v>
+        <v>125017084</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>97231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514351</v>
+        <v>514370</v>
       </c>
       <c r="R7" t="n">
-        <v>6742013</v>
+        <v>6742063</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017081</v>
+        <v>125017085</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514370</v>
+        <v>514342</v>
       </c>
       <c r="R8" t="n">
-        <v>6742029</v>
+        <v>6742146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017047</v>
+        <v>125017082</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,34 +1370,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514334</v>
+        <v>514343</v>
       </c>
       <c r="R9" t="n">
-        <v>6741981</v>
+        <v>6741717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017021</v>
+        <v>125017016</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514291</v>
+        <v>514278</v>
       </c>
       <c r="R10" t="n">
-        <v>6741927</v>
+        <v>6741831</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017013</v>
+        <v>125017040</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514345</v>
+        <v>514327</v>
       </c>
       <c r="R11" t="n">
-        <v>6741942</v>
+        <v>6741885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1624,6 +1633,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,14 +1664,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017070</v>
+        <v>125017041</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1685,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514333</v>
+        <v>514235</v>
       </c>
       <c r="R12" t="n">
-        <v>6741764</v>
+        <v>6742182</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,14 +1761,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017075</v>
+        <v>125017042</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1782,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514356</v>
+        <v>514331</v>
       </c>
       <c r="R13" t="n">
-        <v>6742004</v>
+        <v>6742061</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,14 +1858,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017042</v>
+        <v>125017043</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1879,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514331</v>
+        <v>514354</v>
       </c>
       <c r="R14" t="n">
-        <v>6742061</v>
+        <v>6742044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,14 +1955,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017051</v>
+        <v>125017044</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1976,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514337</v>
+        <v>514351</v>
       </c>
       <c r="R15" t="n">
-        <v>6741897</v>
+        <v>6742013</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,14 +2052,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017048</v>
+        <v>125017045</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2073,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514295</v>
+        <v>514340</v>
       </c>
       <c r="R16" t="n">
-        <v>6741934</v>
+        <v>6741996</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,14 +2149,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017078</v>
+        <v>125017046</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2170,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514359</v>
+        <v>514337</v>
       </c>
       <c r="R17" t="n">
-        <v>6742012</v>
+        <v>6741991</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017083</v>
+        <v>125017047</v>
       </c>
       <c r="B18" t="n">
-        <v>96395</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514373</v>
+        <v>514334</v>
       </c>
       <c r="R18" t="n">
-        <v>6741951</v>
+        <v>6741981</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,14 +2343,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017049</v>
+        <v>125017048</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2364,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514311</v>
+        <v>514295</v>
       </c>
       <c r="R19" t="n">
-        <v>6741920</v>
+        <v>6741934</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,50 +2440,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017031</v>
+        <v>125017049</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514358</v>
+        <v>514311</v>
       </c>
       <c r="R20" t="n">
-        <v>6741952</v>
+        <v>6741920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,32 +2537,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017085</v>
+        <v>125017050</v>
       </c>
       <c r="B21" t="n">
-        <v>96395</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2572,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514342</v>
+        <v>514318</v>
       </c>
       <c r="R21" t="n">
-        <v>6742146</v>
+        <v>6741915</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,32 +2634,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017025</v>
+        <v>125017051</v>
       </c>
       <c r="B22" t="n">
-        <v>91166</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514390</v>
+        <v>514337</v>
       </c>
       <c r="R22" t="n">
-        <v>6741952</v>
+        <v>6741897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,14 +2731,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017071</v>
+        <v>125017052</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2757,10 +2766,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514339</v>
+        <v>514274</v>
       </c>
       <c r="R23" t="n">
-        <v>6741763</v>
+        <v>6741848</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,14 +2828,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017041</v>
+        <v>125017053</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2854,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514235</v>
+        <v>514273</v>
       </c>
       <c r="R24" t="n">
-        <v>6742182</v>
+        <v>6741841</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,14 +2925,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017069</v>
+        <v>125017054</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2951,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514232</v>
+        <v>514257</v>
       </c>
       <c r="R25" t="n">
-        <v>6741754</v>
+        <v>6741839</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,14 +3022,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017072</v>
+        <v>125017055</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3048,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514411</v>
+        <v>514243</v>
       </c>
       <c r="R26" t="n">
-        <v>6741898</v>
+        <v>6741837</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,54 +3119,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017082</v>
+        <v>125017069</v>
       </c>
       <c r="B27" t="n">
-        <v>92448</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514343</v>
+        <v>514232</v>
       </c>
       <c r="R27" t="n">
-        <v>6741717</v>
+        <v>6741754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,14 +3216,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017055</v>
+        <v>125017070</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514243</v>
+        <v>514333</v>
       </c>
       <c r="R28" t="n">
-        <v>6741837</v>
+        <v>6741764</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3313,14 +3313,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017053</v>
+        <v>125017071</v>
       </c>
       <c r="B29" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514273</v>
+        <v>514339</v>
       </c>
       <c r="R29" t="n">
-        <v>6741841</v>
+        <v>6741763</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3410,32 +3410,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017037</v>
+        <v>125017072</v>
       </c>
       <c r="B30" t="n">
-        <v>91184</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514291</v>
+        <v>514411</v>
       </c>
       <c r="R30" t="n">
-        <v>6741924</v>
+        <v>6741898</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3507,32 +3507,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017015</v>
+        <v>125017073</v>
       </c>
       <c r="B31" t="n">
-        <v>96522</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514225</v>
+        <v>514387</v>
       </c>
       <c r="R31" t="n">
-        <v>6741799</v>
+        <v>6741982</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3578,11 +3578,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3609,50 +3604,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017033</v>
+        <v>125017074</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514336</v>
+        <v>514374</v>
       </c>
       <c r="R32" t="n">
-        <v>6741710</v>
+        <v>6741981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,50 +3701,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017035</v>
+        <v>125017075</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514366</v>
+        <v>514356</v>
       </c>
       <c r="R33" t="n">
-        <v>6741941</v>
+        <v>6742004</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,32 +3798,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017087</v>
+        <v>125017076</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3833,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514358</v>
+        <v>514359</v>
       </c>
       <c r="R34" t="n">
-        <v>6742011</v>
+        <v>6742010</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3910,32 +3895,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017086</v>
+        <v>125017078</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3930,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514306</v>
+        <v>514359</v>
       </c>
       <c r="R35" t="n">
-        <v>6741916</v>
+        <v>6742012</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4010,11 +3995,11 @@
         <v>125017080</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4104,50 +4089,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017030</v>
+        <v>125017081</v>
       </c>
       <c r="B37" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514354</v>
+        <v>514370</v>
       </c>
       <c r="R37" t="n">
-        <v>6741952</v>
+        <v>6742029</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4209,7 +4189,7 @@
         <v>125017014</v>
       </c>
       <c r="B38" t="n">
-        <v>75025</v>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4303,10 +4283,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017076</v>
+        <v>125017013</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,21 +4294,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4338,10 +4318,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514359</v>
+        <v>514345</v>
       </c>
       <c r="R39" t="n">
-        <v>6742010</v>
+        <v>6741942</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4400,32 +4380,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017046</v>
+        <v>125017086</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
+        <v>5179</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4435,10 +4415,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514337</v>
+        <v>514306</v>
       </c>
       <c r="R40" t="n">
-        <v>6741991</v>
+        <v>6741916</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4497,54 +4477,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017036</v>
+        <v>125017087</v>
       </c>
       <c r="B41" t="n">
-        <v>98269</v>
+        <v>5179</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514293</v>
+        <v>514358</v>
       </c>
       <c r="R41" t="n">
-        <v>6742097</v>
+        <v>6742011</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4603,32 +4574,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017022</v>
+        <v>125017088</v>
       </c>
       <c r="B42" t="n">
-        <v>91166</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4609,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514283</v>
+        <v>514339</v>
       </c>
       <c r="R42" t="n">
-        <v>6741836</v>
+        <v>6741763</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4700,45 +4671,59 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017016</v>
+        <v>128076199</v>
       </c>
       <c r="B43" t="n">
-        <v>91131</v>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tamptjärnsån, Dlr</t>
+          <t>Tamptjärnsån, Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514278</v>
+        <v>514281</v>
       </c>
       <c r="R43" t="n">
-        <v>6741831</v>
+        <v>6742166</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4765,12 +4750,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4785,22 +4780,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017032</v>
+        <v>125017029</v>
       </c>
       <c r="B44" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4828,7 +4823,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4837,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514330</v>
+        <v>514393</v>
       </c>
       <c r="R44" t="n">
-        <v>6741874</v>
+        <v>6741939</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,45 +4894,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017054</v>
+        <v>125017030</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514257</v>
+        <v>514354</v>
       </c>
       <c r="R45" t="n">
-        <v>6741839</v>
+        <v>6741952</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,45 +4996,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017052</v>
+        <v>125017031</v>
       </c>
       <c r="B46" t="n">
-        <v>78947</v>
+        <v>8455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514274</v>
+        <v>514358</v>
       </c>
       <c r="R46" t="n">
-        <v>6741848</v>
+        <v>6741952</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,45 +5098,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017073</v>
+        <v>125017032</v>
       </c>
       <c r="B47" t="n">
-        <v>78947</v>
+        <v>8455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514387</v>
+        <v>514330</v>
       </c>
       <c r="R47" t="n">
-        <v>6741982</v>
+        <v>6741874</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5190,10 +5200,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017088</v>
+        <v>125017033</v>
       </c>
       <c r="B48" t="n">
-        <v>5176</v>
+        <v>8455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5201,34 +5211,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514339</v>
+        <v>514336</v>
       </c>
       <c r="R48" t="n">
-        <v>6741763</v>
+        <v>6741710</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5287,45 +5302,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017040</v>
+        <v>125017034</v>
       </c>
       <c r="B49" t="n">
-        <v>78947</v>
+        <v>8455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514327</v>
+        <v>514346</v>
       </c>
       <c r="R49" t="n">
-        <v>6741885</v>
+        <v>6741714</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5358,11 +5378,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5389,10 +5404,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017034</v>
+        <v>125017035</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,10 +5444,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514346</v>
+        <v>514366</v>
       </c>
       <c r="R50" t="n">
-        <v>6741714</v>
+        <v>6741941</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5491,45 +5506,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017027</v>
+        <v>125017036</v>
       </c>
       <c r="B51" t="n">
-        <v>97147</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514325</v>
+        <v>514293</v>
       </c>
       <c r="R51" t="n">
-        <v>6742071</v>
+        <v>6742097</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5588,32 +5612,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017050</v>
+        <v>125017027</v>
       </c>
       <c r="B52" t="n">
-        <v>78947</v>
+        <v>97983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5623,10 +5647,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514318</v>
+        <v>514325</v>
       </c>
       <c r="R52" t="n">
-        <v>6741915</v>
+        <v>6742071</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5685,59 +5709,40 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128076199</v>
+        <v>125017089</v>
       </c>
       <c r="B53" t="n">
-        <v>57849</v>
+        <v>92285</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6331024</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis delicata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tamptjärnsån, Tamptjärnsån, Dlr</t>
+          <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
         <v>514281</v>
       </c>
       <c r="R53" t="n">
-        <v>6742166</v>
+        <v>6741837</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5764,42 +5769,38 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Blek fruktkropp med uppslitsade, oregelbundna kantiga porer på gammal ullticka i sumpskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 35314-2025 artfynd.xlsx
+++ b/artfynd/A 35314-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017015</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017021</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017083</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017084</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017016</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017040</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017042</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017043</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1855,6 +1915,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017044</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017045</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017046</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2146,6 +2221,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017047</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017048</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2340,6 +2425,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017049</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2437,6 +2527,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017050</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017051</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2631,6 +2731,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017052</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2728,6 +2833,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017053</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2825,6 +2935,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017054</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2922,6 +3037,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017055</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3019,6 +3139,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017069</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3116,6 +3241,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017070</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3213,6 +3343,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017071</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3310,6 +3445,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017072</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3407,6 +3547,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017073</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3504,6 +3649,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017074</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3601,6 +3751,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017075</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3698,6 +3853,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017076</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3795,6 +3955,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017078</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3892,6 +4057,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017080</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3989,6 +4159,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017081</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4086,6 +4261,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017014</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4183,6 +4363,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017013</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4280,6 +4465,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017086</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4377,6 +4567,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017087</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4474,6 +4669,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017088</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4576,6 +4776,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017029</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4678,6 +4883,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017030</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4780,6 +4990,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017031</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4882,6 +5097,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017032</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4984,6 +5204,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017033</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5086,6 +5311,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017034</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5188,6 +5418,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017035</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5294,6 +5529,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017036</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5391,6 +5631,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017027</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5489,6 +5734,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017089</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5586,6 +5836,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017085</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5683,6 +5938,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017041</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5804,8 +6064,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128076199</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>